--- a/results/02_taxa_assemblage/WardsClustering/tables/anova_env.xlsx
+++ b/results/02_taxa_assemblage/WardsClustering/tables/anova_env.xlsx
@@ -490,38 +490,38 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>149.57</v>
+        <v>220.95</v>
       </c>
       <c r="D2" t="n">
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>377.02</v>
+        <v>305.64</v>
       </c>
       <c r="F2" t="n">
         <v>47</v>
       </c>
       <c r="G2" t="n">
-        <v>9.32</v>
+        <v>16.99</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.0004***</t>
+          <t>0.0000***</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.54 ± 0.44</t>
+          <t>3.05 ± 0.48</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6.82 ± 1.00</t>
+          <t>8.47 ± 0.96</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>3.46 ± 0.71</t>
+          <t>2.85 ± 0.55</t>
         </is>
       </c>
     </row>
@@ -531,42 +531,42 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MPS (Phi)</t>
+          <t>Temperature (oC)</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.6</v>
+        <v>70</v>
       </c>
       <c r="D3" t="n">
         <v>2</v>
       </c>
       <c r="E3" t="n">
-        <v>18.03</v>
+        <v>182.65</v>
       </c>
       <c r="F3" t="n">
         <v>47</v>
       </c>
       <c r="G3" t="n">
-        <v>3.39</v>
+        <v>9.01</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.0421*</t>
+          <t>0.0005***</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>1.30 ± 0.10</t>
+          <t>19.64 ± 0.31</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.78 ± 0.22</t>
+          <t>17.92 ± 0.87</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>1.30 ± 0.16</t>
+          <t>21.74 ± 0.65</t>
         </is>
       </c>
     </row>
@@ -576,42 +576,42 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Temperature (oC)</t>
+          <t>MPS (Phi)</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>18.37</v>
+        <v>5.36</v>
       </c>
       <c r="D4" t="n">
         <v>2</v>
       </c>
       <c r="E4" t="n">
-        <v>234.28</v>
+        <v>15.27</v>
       </c>
       <c r="F4" t="n">
         <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>1.84</v>
+        <v>8.24</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.1696</t>
+          <t>0.0009***</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>19.51 ± 0.41</t>
+          <t>1.28 ± 0.10</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>19.04 ± 0.77</t>
+          <t>0.48 ± 0.25</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>20.52 ± 0.53</t>
+          <t>1.44 ± 0.08</t>
         </is>
       </c>
     </row>
@@ -625,38 +625,38 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1.26</v>
+        <v>1.24</v>
       </c>
       <c r="D5" t="n">
         <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>56.1</v>
+        <v>56.12</v>
       </c>
       <c r="F5" t="n">
         <v>47</v>
       </c>
       <c r="G5" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.5924</t>
+          <t>0.5981</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1.31 ± 0.13</t>
+          <t>1.53 ± 0.23</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1.44 ± 0.24</t>
+          <t>1.64 ± 0.31</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>1.68 ± 0.37</t>
+          <t>1.17 ± 0.13</t>
         </is>
       </c>
     </row>
@@ -670,38 +670,38 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.39</v>
+        <v>0.06</v>
       </c>
       <c r="D6" t="n">
         <v>2</v>
       </c>
       <c r="E6" t="n">
-        <v>90.01000000000001</v>
+        <v>90.34</v>
       </c>
       <c r="F6" t="n">
         <v>47</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.9030</t>
+          <t>0.9841</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>9.48 ± 0.28</t>
+          <t>9.42 ± 0.21</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9.26 ± 0.51</t>
+          <t>9.33 ± 0.67</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>9.42 ± 0.27</t>
+          <t>9.38 ± 0.46</t>
         </is>
       </c>
     </row>
@@ -736,13 +736,13 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J8" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="K8" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9">
